--- a/june 2026/LMT_JUNE_26/Rainbow/Rainbow Cash & Carry Shadra.xlsx
+++ b/june 2026/LMT_JUNE_26/Rainbow/Rainbow Cash & Carry Shadra.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEE01CAD-2FE6-4CE0-8B73-983571041CEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04FCF9CA-DA73-4CB2-9276-801DAA74DAB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="949" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -76,7 +76,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1580" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1581" uniqueCount="108">
   <si>
     <t>Gm</t>
   </si>
@@ -390,9 +390,6 @@
     <t>Customer Name : Rainbow Cash &amp; Carry</t>
   </si>
   <si>
-    <t>Address: Shadra</t>
-  </si>
-  <si>
     <t>Shop Bill Summary (Shahdra (Rainbow)</t>
   </si>
   <si>
@@ -400,6 +397,9 @@
   </si>
   <si>
     <t>\</t>
+  </si>
+  <si>
+    <t>Address: Model Town</t>
   </si>
 </sst>
 </file>
@@ -3382,7 +3382,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46206</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -3410,7 +3410,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46196</v>
+        <v>46205</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
@@ -3419,7 +3419,7 @@
     </row>
     <row r="6" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="230" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B6" s="230"/>
       <c r="C6" s="230"/>
@@ -3702,18 +3702,14 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G16" s="99"/>
-      <c r="H16" s="100">
-        <v>0</v>
-      </c>
+      <c r="H16" s="100"/>
       <c r="I16" s="101">
         <f>(G16*D16)*F16+H16*F16</f>
         <v>0</v>
       </c>
-      <c r="J16" s="102">
-        <v>0</v>
-      </c>
+      <c r="J16" s="102"/>
       <c r="K16" s="103">
-        <f>I16*$K$13</f>
+        <f>I16*3.5%</f>
         <v>0</v>
       </c>
       <c r="L16" s="104">
@@ -3766,18 +3762,14 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G17" s="113"/>
-      <c r="H17" s="114">
-        <v>0</v>
-      </c>
+      <c r="H17" s="114"/>
       <c r="I17" s="115">
         <f t="shared" ref="I17:I23" si="2">(G17*D17)*F17+H17*F17</f>
         <v>0</v>
       </c>
-      <c r="J17" s="116">
-        <v>0</v>
-      </c>
-      <c r="K17" s="1">
-        <f t="shared" ref="K17:K21" si="3">I17*$K$13</f>
+      <c r="J17" s="116"/>
+      <c r="K17" s="103">
+        <f t="shared" ref="K17:K21" si="3">I17*3.5%</f>
         <v>0</v>
       </c>
       <c r="L17" s="104">
@@ -3830,17 +3822,13 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G18" s="113"/>
-      <c r="H18" s="114">
-        <v>0</v>
-      </c>
+      <c r="H18" s="114"/>
       <c r="I18" s="115">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J18" s="116">
-        <v>0</v>
-      </c>
-      <c r="K18" s="1">
+      <c r="J18" s="116"/>
+      <c r="K18" s="103">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -3890,17 +3878,13 @@
         <v>72.64</v>
       </c>
       <c r="G19" s="113"/>
-      <c r="H19" s="114">
-        <v>0</v>
-      </c>
+      <c r="H19" s="114"/>
       <c r="I19" s="115">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J19" s="116">
-        <v>0</v>
-      </c>
-      <c r="K19" s="1">
+      <c r="J19" s="116"/>
+      <c r="K19" s="103">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -3950,17 +3934,13 @@
         <v>72.64</v>
       </c>
       <c r="G20" s="113"/>
-      <c r="H20" s="114">
-        <v>0</v>
-      </c>
+      <c r="H20" s="114"/>
       <c r="I20" s="115">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J20" s="116">
-        <v>0</v>
-      </c>
-      <c r="K20" s="1">
+      <c r="J20" s="116"/>
+      <c r="K20" s="103">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -4010,17 +3990,13 @@
         <v>72.64</v>
       </c>
       <c r="G21" s="113"/>
-      <c r="H21" s="114">
-        <v>0</v>
-      </c>
+      <c r="H21" s="114"/>
       <c r="I21" s="115">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J21" s="116">
-        <v>0</v>
-      </c>
-      <c r="K21" s="1">
+      <c r="J21" s="116"/>
+      <c r="K21" s="103">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -4627,7 +4603,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46206</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -4655,7 +4631,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46196</v>
+        <v>46205</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
@@ -4664,7 +4640,7 @@
     </row>
     <row r="6" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="230" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B6" s="230"/>
       <c r="C6" s="230"/>
@@ -4947,18 +4923,14 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G16" s="99"/>
-      <c r="H16" s="100">
-        <v>0</v>
-      </c>
+      <c r="H16" s="100"/>
       <c r="I16" s="101">
         <f>(G16*D16)*F16+H16*F16</f>
         <v>0</v>
       </c>
-      <c r="J16" s="102">
-        <v>0</v>
-      </c>
+      <c r="J16" s="102"/>
       <c r="K16" s="103">
-        <f>I16*$K$13</f>
+        <f>I16*3.5%</f>
         <v>0</v>
       </c>
       <c r="L16" s="104">
@@ -5011,18 +4983,14 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G17" s="113"/>
-      <c r="H17" s="114">
-        <v>0</v>
-      </c>
+      <c r="H17" s="114"/>
       <c r="I17" s="115">
         <f t="shared" ref="I17:I23" si="2">(G17*D17)*F17+H17*F17</f>
         <v>0</v>
       </c>
-      <c r="J17" s="116">
-        <v>0</v>
-      </c>
-      <c r="K17" s="1">
-        <f t="shared" ref="K17:K21" si="3">I17*$K$13</f>
+      <c r="J17" s="116"/>
+      <c r="K17" s="103">
+        <f t="shared" ref="K17:K21" si="3">I17*3.5%</f>
         <v>0</v>
       </c>
       <c r="L17" s="104">
@@ -5075,17 +5043,13 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G18" s="113"/>
-      <c r="H18" s="114">
-        <v>0</v>
-      </c>
+      <c r="H18" s="114"/>
       <c r="I18" s="115">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J18" s="116">
-        <v>0</v>
-      </c>
-      <c r="K18" s="1">
+      <c r="J18" s="116"/>
+      <c r="K18" s="103">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -5135,17 +5099,13 @@
         <v>72.64</v>
       </c>
       <c r="G19" s="113"/>
-      <c r="H19" s="114">
-        <v>0</v>
-      </c>
+      <c r="H19" s="114"/>
       <c r="I19" s="115">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J19" s="116">
-        <v>0</v>
-      </c>
-      <c r="K19" s="1">
+      <c r="J19" s="116"/>
+      <c r="K19" s="103">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -5195,17 +5155,13 @@
         <v>72.64</v>
       </c>
       <c r="G20" s="113"/>
-      <c r="H20" s="114">
-        <v>0</v>
-      </c>
+      <c r="H20" s="114"/>
       <c r="I20" s="115">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J20" s="116">
-        <v>0</v>
-      </c>
-      <c r="K20" s="1">
+      <c r="J20" s="116"/>
+      <c r="K20" s="103">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -5255,17 +5211,13 @@
         <v>72.64</v>
       </c>
       <c r="G21" s="113"/>
-      <c r="H21" s="114">
-        <v>0</v>
-      </c>
+      <c r="H21" s="114"/>
       <c r="I21" s="115">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J21" s="116">
-        <v>0</v>
-      </c>
-      <c r="K21" s="1">
+      <c r="J21" s="116"/>
+      <c r="K21" s="103">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -5872,7 +5824,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46206</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -5900,7 +5852,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46196</v>
+        <v>46205</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
@@ -5909,7 +5861,7 @@
     </row>
     <row r="6" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="230" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B6" s="230"/>
       <c r="C6" s="230"/>
@@ -6192,18 +6144,14 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G16" s="99"/>
-      <c r="H16" s="100">
-        <v>0</v>
-      </c>
+      <c r="H16" s="100"/>
       <c r="I16" s="101">
         <f>(G16*D16)*F16+H16*F16</f>
         <v>0</v>
       </c>
-      <c r="J16" s="102">
-        <v>0</v>
-      </c>
+      <c r="J16" s="102"/>
       <c r="K16" s="103">
-        <f>I16*$K$13</f>
+        <f>I16*3.5%</f>
         <v>0</v>
       </c>
       <c r="L16" s="104">
@@ -6256,18 +6204,14 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G17" s="113"/>
-      <c r="H17" s="114">
-        <v>0</v>
-      </c>
+      <c r="H17" s="114"/>
       <c r="I17" s="115">
         <f t="shared" ref="I17:I23" si="2">(G17*D17)*F17+H17*F17</f>
         <v>0</v>
       </c>
-      <c r="J17" s="116">
-        <v>0</v>
-      </c>
-      <c r="K17" s="1">
-        <f t="shared" ref="K17:K21" si="3">I17*$K$13</f>
+      <c r="J17" s="116"/>
+      <c r="K17" s="103">
+        <f t="shared" ref="K17:K21" si="3">I17*3.5%</f>
         <v>0</v>
       </c>
       <c r="L17" s="104">
@@ -6320,17 +6264,13 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G18" s="113"/>
-      <c r="H18" s="114">
-        <v>0</v>
-      </c>
+      <c r="H18" s="114"/>
       <c r="I18" s="115">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J18" s="116">
-        <v>0</v>
-      </c>
-      <c r="K18" s="1">
+      <c r="J18" s="116"/>
+      <c r="K18" s="103">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -6380,17 +6320,13 @@
         <v>72.64</v>
       </c>
       <c r="G19" s="113"/>
-      <c r="H19" s="114">
-        <v>0</v>
-      </c>
+      <c r="H19" s="114"/>
       <c r="I19" s="115">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J19" s="116">
-        <v>0</v>
-      </c>
-      <c r="K19" s="1">
+      <c r="J19" s="116"/>
+      <c r="K19" s="103">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -6440,17 +6376,13 @@
         <v>72.64</v>
       </c>
       <c r="G20" s="113"/>
-      <c r="H20" s="114">
-        <v>0</v>
-      </c>
+      <c r="H20" s="114"/>
       <c r="I20" s="115">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J20" s="116">
-        <v>0</v>
-      </c>
-      <c r="K20" s="1">
+      <c r="J20" s="116"/>
+      <c r="K20" s="103">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -6500,17 +6432,13 @@
         <v>72.64</v>
       </c>
       <c r="G21" s="113"/>
-      <c r="H21" s="114">
-        <v>0</v>
-      </c>
+      <c r="H21" s="114"/>
       <c r="I21" s="115">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J21" s="116">
-        <v>0</v>
-      </c>
-      <c r="K21" s="1">
+      <c r="J21" s="116"/>
+      <c r="K21" s="103">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -7117,7 +7045,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46206</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -7145,7 +7073,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46196</v>
+        <v>46205</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
@@ -7154,7 +7082,7 @@
     </row>
     <row r="6" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="230" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B6" s="230"/>
       <c r="C6" s="230"/>
@@ -7437,18 +7365,14 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G16" s="99"/>
-      <c r="H16" s="100">
-        <v>0</v>
-      </c>
+      <c r="H16" s="100"/>
       <c r="I16" s="101">
         <f>(G16*D16)*F16+H16*F16</f>
         <v>0</v>
       </c>
-      <c r="J16" s="102">
-        <v>0</v>
-      </c>
+      <c r="J16" s="102"/>
       <c r="K16" s="103">
-        <f>I16*$K$13</f>
+        <f>I16*3.5%</f>
         <v>0</v>
       </c>
       <c r="L16" s="104">
@@ -7501,18 +7425,14 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G17" s="113"/>
-      <c r="H17" s="114">
-        <v>0</v>
-      </c>
+      <c r="H17" s="114"/>
       <c r="I17" s="115">
         <f t="shared" ref="I17:I23" si="2">(G17*D17)*F17+H17*F17</f>
         <v>0</v>
       </c>
-      <c r="J17" s="116">
-        <v>0</v>
-      </c>
-      <c r="K17" s="1">
-        <f t="shared" ref="K17:K21" si="3">I17*$K$13</f>
+      <c r="J17" s="116"/>
+      <c r="K17" s="103">
+        <f t="shared" ref="K17:K21" si="3">I17*3.5%</f>
         <v>0</v>
       </c>
       <c r="L17" s="104">
@@ -7565,17 +7485,13 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G18" s="113"/>
-      <c r="H18" s="114">
-        <v>0</v>
-      </c>
+      <c r="H18" s="114"/>
       <c r="I18" s="115">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J18" s="116">
-        <v>0</v>
-      </c>
-      <c r="K18" s="1">
+      <c r="J18" s="116"/>
+      <c r="K18" s="103">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -7625,17 +7541,13 @@
         <v>72.64</v>
       </c>
       <c r="G19" s="113"/>
-      <c r="H19" s="114">
-        <v>0</v>
-      </c>
+      <c r="H19" s="114"/>
       <c r="I19" s="115">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J19" s="116">
-        <v>0</v>
-      </c>
-      <c r="K19" s="1">
+      <c r="J19" s="116"/>
+      <c r="K19" s="103">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -7685,17 +7597,13 @@
         <v>72.64</v>
       </c>
       <c r="G20" s="113"/>
-      <c r="H20" s="114">
-        <v>0</v>
-      </c>
+      <c r="H20" s="114"/>
       <c r="I20" s="115">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J20" s="116">
-        <v>0</v>
-      </c>
-      <c r="K20" s="1">
+      <c r="J20" s="116"/>
+      <c r="K20" s="103">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -7745,17 +7653,13 @@
         <v>72.64</v>
       </c>
       <c r="G21" s="113"/>
-      <c r="H21" s="114">
-        <v>0</v>
-      </c>
+      <c r="H21" s="114"/>
       <c r="I21" s="115">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J21" s="116">
-        <v>0</v>
-      </c>
-      <c r="K21" s="1">
+      <c r="J21" s="116"/>
+      <c r="K21" s="103">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -8362,7 +8266,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46206</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -8390,7 +8294,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46196</v>
+        <v>46205</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
@@ -8399,7 +8303,7 @@
     </row>
     <row r="6" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="230" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B6" s="230"/>
       <c r="C6" s="230"/>
@@ -8682,18 +8586,14 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G16" s="99"/>
-      <c r="H16" s="100">
-        <v>0</v>
-      </c>
+      <c r="H16" s="100"/>
       <c r="I16" s="101">
         <f>(G16*D16)*F16+H16*F16</f>
         <v>0</v>
       </c>
-      <c r="J16" s="102">
-        <v>0</v>
-      </c>
+      <c r="J16" s="102"/>
       <c r="K16" s="103">
-        <f>I16*$K$13</f>
+        <f>I16*3.5%</f>
         <v>0</v>
       </c>
       <c r="L16" s="104">
@@ -8746,18 +8646,14 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G17" s="113"/>
-      <c r="H17" s="114">
-        <v>0</v>
-      </c>
+      <c r="H17" s="114"/>
       <c r="I17" s="115">
         <f t="shared" ref="I17:I23" si="2">(G17*D17)*F17+H17*F17</f>
         <v>0</v>
       </c>
-      <c r="J17" s="116">
-        <v>0</v>
-      </c>
-      <c r="K17" s="1">
-        <f t="shared" ref="K17:K21" si="3">I17*$K$13</f>
+      <c r="J17" s="116"/>
+      <c r="K17" s="103">
+        <f t="shared" ref="K17:K21" si="3">I17*3.5%</f>
         <v>0</v>
       </c>
       <c r="L17" s="104">
@@ -8810,17 +8706,13 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G18" s="113"/>
-      <c r="H18" s="114">
-        <v>0</v>
-      </c>
+      <c r="H18" s="114"/>
       <c r="I18" s="115">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J18" s="116">
-        <v>0</v>
-      </c>
-      <c r="K18" s="1">
+      <c r="J18" s="116"/>
+      <c r="K18" s="103">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -8870,17 +8762,13 @@
         <v>72.64</v>
       </c>
       <c r="G19" s="113"/>
-      <c r="H19" s="114">
-        <v>0</v>
-      </c>
+      <c r="H19" s="114"/>
       <c r="I19" s="115">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J19" s="116">
-        <v>0</v>
-      </c>
-      <c r="K19" s="1">
+      <c r="J19" s="116"/>
+      <c r="K19" s="103">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -8930,17 +8818,13 @@
         <v>72.64</v>
       </c>
       <c r="G20" s="113"/>
-      <c r="H20" s="114">
-        <v>0</v>
-      </c>
+      <c r="H20" s="114"/>
       <c r="I20" s="115">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J20" s="116">
-        <v>0</v>
-      </c>
-      <c r="K20" s="1">
+      <c r="J20" s="116"/>
+      <c r="K20" s="103">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -8990,17 +8874,13 @@
         <v>72.64</v>
       </c>
       <c r="G21" s="113"/>
-      <c r="H21" s="114">
-        <v>0</v>
-      </c>
+      <c r="H21" s="114"/>
       <c r="I21" s="115">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J21" s="116">
-        <v>0</v>
-      </c>
-      <c r="K21" s="1">
+      <c r="J21" s="116"/>
+      <c r="K21" s="103">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -9607,7 +9487,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46206</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -9635,7 +9515,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46196</v>
+        <v>46205</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
@@ -9644,7 +9524,7 @@
     </row>
     <row r="6" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="230" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B6" s="230"/>
       <c r="C6" s="230"/>
@@ -9927,18 +9807,14 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G16" s="99"/>
-      <c r="H16" s="100">
-        <v>0</v>
-      </c>
+      <c r="H16" s="100"/>
       <c r="I16" s="101">
         <f>(G16*D16)*F16+H16*F16</f>
         <v>0</v>
       </c>
-      <c r="J16" s="102">
-        <v>0</v>
-      </c>
+      <c r="J16" s="102"/>
       <c r="K16" s="103">
-        <f>I16*$K$13</f>
+        <f>I16*3.5%</f>
         <v>0</v>
       </c>
       <c r="L16" s="104">
@@ -9991,18 +9867,14 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G17" s="113"/>
-      <c r="H17" s="114">
-        <v>0</v>
-      </c>
+      <c r="H17" s="114"/>
       <c r="I17" s="115">
         <f t="shared" ref="I17:I23" si="2">(G17*D17)*F17+H17*F17</f>
         <v>0</v>
       </c>
-      <c r="J17" s="116">
-        <v>0</v>
-      </c>
-      <c r="K17" s="1">
-        <f t="shared" ref="K17:K21" si="3">I17*$K$13</f>
+      <c r="J17" s="116"/>
+      <c r="K17" s="103">
+        <f t="shared" ref="K17:K21" si="3">I17*3.5%</f>
         <v>0</v>
       </c>
       <c r="L17" s="104">
@@ -10055,17 +9927,13 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G18" s="113"/>
-      <c r="H18" s="114">
-        <v>0</v>
-      </c>
+      <c r="H18" s="114"/>
       <c r="I18" s="115">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J18" s="116">
-        <v>0</v>
-      </c>
-      <c r="K18" s="1">
+      <c r="J18" s="116"/>
+      <c r="K18" s="103">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -10115,17 +9983,13 @@
         <v>72.64</v>
       </c>
       <c r="G19" s="113"/>
-      <c r="H19" s="114">
-        <v>0</v>
-      </c>
+      <c r="H19" s="114"/>
       <c r="I19" s="115">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J19" s="116">
-        <v>0</v>
-      </c>
-      <c r="K19" s="1">
+      <c r="J19" s="116"/>
+      <c r="K19" s="103">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -10175,17 +10039,13 @@
         <v>72.64</v>
       </c>
       <c r="G20" s="113"/>
-      <c r="H20" s="114">
-        <v>0</v>
-      </c>
+      <c r="H20" s="114"/>
       <c r="I20" s="115">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J20" s="116">
-        <v>0</v>
-      </c>
-      <c r="K20" s="1">
+      <c r="J20" s="116"/>
+      <c r="K20" s="103">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -10235,17 +10095,13 @@
         <v>72.64</v>
       </c>
       <c r="G21" s="113"/>
-      <c r="H21" s="114">
-        <v>0</v>
-      </c>
+      <c r="H21" s="114"/>
       <c r="I21" s="115">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J21" s="116">
-        <v>0</v>
-      </c>
-      <c r="K21" s="1">
+      <c r="J21" s="116"/>
+      <c r="K21" s="103">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -10852,7 +10708,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46206</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -10880,7 +10736,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46196</v>
+        <v>46205</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
@@ -10889,7 +10745,7 @@
     </row>
     <row r="6" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="230" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B6" s="230"/>
       <c r="C6" s="230"/>
@@ -11172,18 +11028,14 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G16" s="99"/>
-      <c r="H16" s="100">
-        <v>0</v>
-      </c>
+      <c r="H16" s="100"/>
       <c r="I16" s="101">
         <f>(G16*D16)*F16+H16*F16</f>
         <v>0</v>
       </c>
-      <c r="J16" s="102">
-        <v>0</v>
-      </c>
+      <c r="J16" s="102"/>
       <c r="K16" s="103">
-        <f>I16*$K$13</f>
+        <f>I16*3.5%</f>
         <v>0</v>
       </c>
       <c r="L16" s="104">
@@ -11236,18 +11088,14 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G17" s="113"/>
-      <c r="H17" s="114">
-        <v>0</v>
-      </c>
+      <c r="H17" s="114"/>
       <c r="I17" s="115">
         <f t="shared" ref="I17:I23" si="2">(G17*D17)*F17+H17*F17</f>
         <v>0</v>
       </c>
-      <c r="J17" s="116">
-        <v>0</v>
-      </c>
-      <c r="K17" s="1">
-        <f t="shared" ref="K17:K21" si="3">I17*$K$13</f>
+      <c r="J17" s="116"/>
+      <c r="K17" s="103">
+        <f t="shared" ref="K17:K21" si="3">I17*3.5%</f>
         <v>0</v>
       </c>
       <c r="L17" s="104">
@@ -11300,17 +11148,13 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G18" s="113"/>
-      <c r="H18" s="114">
-        <v>0</v>
-      </c>
+      <c r="H18" s="114"/>
       <c r="I18" s="115">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J18" s="116">
-        <v>0</v>
-      </c>
-      <c r="K18" s="1">
+      <c r="J18" s="116"/>
+      <c r="K18" s="103">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -11360,17 +11204,13 @@
         <v>72.64</v>
       </c>
       <c r="G19" s="113"/>
-      <c r="H19" s="114">
-        <v>0</v>
-      </c>
+      <c r="H19" s="114"/>
       <c r="I19" s="115">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J19" s="116">
-        <v>0</v>
-      </c>
-      <c r="K19" s="1">
+      <c r="J19" s="116"/>
+      <c r="K19" s="103">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -11420,17 +11260,13 @@
         <v>72.64</v>
       </c>
       <c r="G20" s="113"/>
-      <c r="H20" s="114">
-        <v>0</v>
-      </c>
+      <c r="H20" s="114"/>
       <c r="I20" s="115">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J20" s="116">
-        <v>0</v>
-      </c>
-      <c r="K20" s="1">
+      <c r="J20" s="116"/>
+      <c r="K20" s="103">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -11480,17 +11316,13 @@
         <v>72.64</v>
       </c>
       <c r="G21" s="113"/>
-      <c r="H21" s="114">
-        <v>0</v>
-      </c>
+      <c r="H21" s="114"/>
       <c r="I21" s="115">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J21" s="116">
-        <v>0</v>
-      </c>
-      <c r="K21" s="1">
+      <c r="J21" s="116"/>
+      <c r="K21" s="103">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -12097,7 +11929,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46206</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -12125,7 +11957,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46196</v>
+        <v>46205</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
@@ -12134,7 +11966,7 @@
     </row>
     <row r="6" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="230" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B6" s="230"/>
       <c r="C6" s="230"/>
@@ -12417,18 +12249,14 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G16" s="99"/>
-      <c r="H16" s="100">
-        <v>0</v>
-      </c>
+      <c r="H16" s="100"/>
       <c r="I16" s="101">
         <f>(G16*D16)*F16+H16*F16</f>
         <v>0</v>
       </c>
-      <c r="J16" s="102">
-        <v>0</v>
-      </c>
+      <c r="J16" s="102"/>
       <c r="K16" s="103">
-        <f>I16*$K$13</f>
+        <f>I16*3.5%</f>
         <v>0</v>
       </c>
       <c r="L16" s="104">
@@ -12481,18 +12309,14 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G17" s="113"/>
-      <c r="H17" s="114">
-        <v>0</v>
-      </c>
+      <c r="H17" s="114"/>
       <c r="I17" s="115">
         <f t="shared" ref="I17:I23" si="2">(G17*D17)*F17+H17*F17</f>
         <v>0</v>
       </c>
-      <c r="J17" s="116">
-        <v>0</v>
-      </c>
-      <c r="K17" s="1">
-        <f t="shared" ref="K17:K21" si="3">I17*$K$13</f>
+      <c r="J17" s="116"/>
+      <c r="K17" s="103">
+        <f t="shared" ref="K17:K21" si="3">I17*3.5%</f>
         <v>0</v>
       </c>
       <c r="L17" s="104">
@@ -12545,17 +12369,13 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G18" s="113"/>
-      <c r="H18" s="114">
-        <v>0</v>
-      </c>
+      <c r="H18" s="114"/>
       <c r="I18" s="115">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J18" s="116">
-        <v>0</v>
-      </c>
-      <c r="K18" s="1">
+      <c r="J18" s="116"/>
+      <c r="K18" s="103">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -12605,17 +12425,13 @@
         <v>72.64</v>
       </c>
       <c r="G19" s="113"/>
-      <c r="H19" s="114">
-        <v>0</v>
-      </c>
+      <c r="H19" s="114"/>
       <c r="I19" s="115">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J19" s="116">
-        <v>0</v>
-      </c>
-      <c r="K19" s="1">
+      <c r="J19" s="116"/>
+      <c r="K19" s="103">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -12665,17 +12481,13 @@
         <v>72.64</v>
       </c>
       <c r="G20" s="113"/>
-      <c r="H20" s="114">
-        <v>0</v>
-      </c>
+      <c r="H20" s="114"/>
       <c r="I20" s="115">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J20" s="116">
-        <v>0</v>
-      </c>
-      <c r="K20" s="1">
+      <c r="J20" s="116"/>
+      <c r="K20" s="103">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -12725,17 +12537,13 @@
         <v>72.64</v>
       </c>
       <c r="G21" s="113"/>
-      <c r="H21" s="114">
-        <v>0</v>
-      </c>
+      <c r="H21" s="114"/>
       <c r="I21" s="115">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J21" s="116">
-        <v>0</v>
-      </c>
-      <c r="K21" s="1">
+      <c r="J21" s="116"/>
+      <c r="K21" s="103">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -13342,7 +13150,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46206</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -13370,7 +13178,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46196</v>
+        <v>46205</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
@@ -13379,7 +13187,7 @@
     </row>
     <row r="6" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="230" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B6" s="230"/>
       <c r="C6" s="230"/>
@@ -13662,18 +13470,14 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G16" s="99"/>
-      <c r="H16" s="100">
-        <v>0</v>
-      </c>
+      <c r="H16" s="100"/>
       <c r="I16" s="101">
         <f>(G16*D16)*F16+H16*F16</f>
         <v>0</v>
       </c>
-      <c r="J16" s="102">
-        <v>0</v>
-      </c>
+      <c r="J16" s="102"/>
       <c r="K16" s="103">
-        <f>I16*$K$13</f>
+        <f>I16*3.5%</f>
         <v>0</v>
       </c>
       <c r="L16" s="104">
@@ -13726,18 +13530,14 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G17" s="113"/>
-      <c r="H17" s="114">
-        <v>0</v>
-      </c>
+      <c r="H17" s="114"/>
       <c r="I17" s="115">
         <f t="shared" ref="I17:I23" si="2">(G17*D17)*F17+H17*F17</f>
         <v>0</v>
       </c>
-      <c r="J17" s="116">
-        <v>0</v>
-      </c>
-      <c r="K17" s="1">
-        <f t="shared" ref="K17:K21" si="3">I17*$K$13</f>
+      <c r="J17" s="116"/>
+      <c r="K17" s="103">
+        <f t="shared" ref="K17:K21" si="3">I17*3.5%</f>
         <v>0</v>
       </c>
       <c r="L17" s="104">
@@ -13790,17 +13590,13 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G18" s="113"/>
-      <c r="H18" s="114">
-        <v>0</v>
-      </c>
+      <c r="H18" s="114"/>
       <c r="I18" s="115">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J18" s="116">
-        <v>0</v>
-      </c>
-      <c r="K18" s="1">
+      <c r="J18" s="116"/>
+      <c r="K18" s="103">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -13850,17 +13646,13 @@
         <v>72.64</v>
       </c>
       <c r="G19" s="113"/>
-      <c r="H19" s="114">
-        <v>0</v>
-      </c>
+      <c r="H19" s="114"/>
       <c r="I19" s="115">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J19" s="116">
-        <v>0</v>
-      </c>
-      <c r="K19" s="1">
+      <c r="J19" s="116"/>
+      <c r="K19" s="103">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -13910,17 +13702,13 @@
         <v>72.64</v>
       </c>
       <c r="G20" s="113"/>
-      <c r="H20" s="114">
-        <v>0</v>
-      </c>
+      <c r="H20" s="114"/>
       <c r="I20" s="115">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J20" s="116">
-        <v>0</v>
-      </c>
-      <c r="K20" s="1">
+      <c r="J20" s="116"/>
+      <c r="K20" s="103">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -13970,17 +13758,13 @@
         <v>72.64</v>
       </c>
       <c r="G21" s="113"/>
-      <c r="H21" s="114">
-        <v>0</v>
-      </c>
+      <c r="H21" s="114"/>
       <c r="I21" s="115">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J21" s="116">
-        <v>0</v>
-      </c>
-      <c r="K21" s="1">
+      <c r="J21" s="116"/>
+      <c r="K21" s="103">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -14587,7 +14371,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46206</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -14615,7 +14399,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46196</v>
+        <v>46205</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
@@ -14624,7 +14408,7 @@
     </row>
     <row r="6" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="230" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B6" s="230"/>
       <c r="C6" s="230"/>
@@ -14907,18 +14691,14 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G16" s="99"/>
-      <c r="H16" s="100">
-        <v>0</v>
-      </c>
+      <c r="H16" s="100"/>
       <c r="I16" s="101">
         <f>(G16*D16)*F16+H16*F16</f>
         <v>0</v>
       </c>
-      <c r="J16" s="102">
-        <v>0</v>
-      </c>
+      <c r="J16" s="102"/>
       <c r="K16" s="103">
-        <f>I16*$K$13</f>
+        <f>I16*3.5%</f>
         <v>0</v>
       </c>
       <c r="L16" s="104">
@@ -14971,18 +14751,14 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G17" s="113"/>
-      <c r="H17" s="114">
-        <v>0</v>
-      </c>
+      <c r="H17" s="114"/>
       <c r="I17" s="115">
         <f t="shared" ref="I17:I23" si="2">(G17*D17)*F17+H17*F17</f>
         <v>0</v>
       </c>
-      <c r="J17" s="116">
-        <v>0</v>
-      </c>
-      <c r="K17" s="1">
-        <f t="shared" ref="K17:K21" si="3">I17*$K$13</f>
+      <c r="J17" s="116"/>
+      <c r="K17" s="103">
+        <f t="shared" ref="K17:K21" si="3">I17*3.5%</f>
         <v>0</v>
       </c>
       <c r="L17" s="104">
@@ -15035,17 +14811,13 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G18" s="113"/>
-      <c r="H18" s="114">
-        <v>0</v>
-      </c>
+      <c r="H18" s="114"/>
       <c r="I18" s="115">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J18" s="116">
-        <v>0</v>
-      </c>
-      <c r="K18" s="1">
+      <c r="J18" s="116"/>
+      <c r="K18" s="103">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -15095,17 +14867,13 @@
         <v>72.64</v>
       </c>
       <c r="G19" s="113"/>
-      <c r="H19" s="114">
-        <v>0</v>
-      </c>
+      <c r="H19" s="114"/>
       <c r="I19" s="115">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J19" s="116">
-        <v>0</v>
-      </c>
-      <c r="K19" s="1">
+      <c r="J19" s="116"/>
+      <c r="K19" s="103">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -15155,17 +14923,13 @@
         <v>72.64</v>
       </c>
       <c r="G20" s="113"/>
-      <c r="H20" s="114">
-        <v>0</v>
-      </c>
+      <c r="H20" s="114"/>
       <c r="I20" s="115">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J20" s="116">
-        <v>0</v>
-      </c>
-      <c r="K20" s="1">
+      <c r="J20" s="116"/>
+      <c r="K20" s="103">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -15215,17 +14979,13 @@
         <v>72.64</v>
       </c>
       <c r="G21" s="113"/>
-      <c r="H21" s="114">
-        <v>0</v>
-      </c>
+      <c r="H21" s="114"/>
       <c r="I21" s="115">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J21" s="116">
-        <v>0</v>
-      </c>
-      <c r="K21" s="1">
+      <c r="J21" s="116"/>
+      <c r="K21" s="103">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -18582,7 +18342,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46206</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -18610,7 +18370,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46196</v>
+        <v>46205</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
@@ -18619,7 +18379,7 @@
     </row>
     <row r="6" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="230" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B6" s="230"/>
       <c r="C6" s="230"/>
@@ -18902,18 +18662,14 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G16" s="99"/>
-      <c r="H16" s="100">
-        <v>0</v>
-      </c>
+      <c r="H16" s="100"/>
       <c r="I16" s="101">
         <f>(G16*D16)*F16+H16*F16</f>
         <v>0</v>
       </c>
-      <c r="J16" s="102">
-        <v>0</v>
-      </c>
+      <c r="J16" s="102"/>
       <c r="K16" s="103">
-        <f>I16*$K$13</f>
+        <f>I16*3.5%</f>
         <v>0</v>
       </c>
       <c r="L16" s="104">
@@ -18966,18 +18722,14 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G17" s="113"/>
-      <c r="H17" s="114">
-        <v>0</v>
-      </c>
+      <c r="H17" s="114"/>
       <c r="I17" s="115">
         <f t="shared" ref="I17:I23" si="2">(G17*D17)*F17+H17*F17</f>
         <v>0</v>
       </c>
-      <c r="J17" s="116">
-        <v>0</v>
-      </c>
-      <c r="K17" s="1">
-        <f t="shared" ref="K17:K21" si="3">I17*$K$13</f>
+      <c r="J17" s="116"/>
+      <c r="K17" s="103">
+        <f t="shared" ref="K17:K21" si="3">I17*3.5%</f>
         <v>0</v>
       </c>
       <c r="L17" s="104">
@@ -19030,17 +18782,13 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G18" s="113"/>
-      <c r="H18" s="114">
-        <v>0</v>
-      </c>
+      <c r="H18" s="114"/>
       <c r="I18" s="115">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J18" s="116">
-        <v>0</v>
-      </c>
-      <c r="K18" s="1">
+      <c r="J18" s="116"/>
+      <c r="K18" s="103">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -19090,17 +18838,13 @@
         <v>72.64</v>
       </c>
       <c r="G19" s="113"/>
-      <c r="H19" s="114">
-        <v>0</v>
-      </c>
+      <c r="H19" s="114"/>
       <c r="I19" s="115">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J19" s="116">
-        <v>0</v>
-      </c>
-      <c r="K19" s="1">
+      <c r="J19" s="116"/>
+      <c r="K19" s="103">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -19150,17 +18894,13 @@
         <v>72.64</v>
       </c>
       <c r="G20" s="113"/>
-      <c r="H20" s="114">
-        <v>0</v>
-      </c>
+      <c r="H20" s="114"/>
       <c r="I20" s="115">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J20" s="116">
-        <v>0</v>
-      </c>
-      <c r="K20" s="1">
+      <c r="J20" s="116"/>
+      <c r="K20" s="103">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -19210,17 +18950,13 @@
         <v>72.64</v>
       </c>
       <c r="G21" s="113"/>
-      <c r="H21" s="114">
-        <v>0</v>
-      </c>
+      <c r="H21" s="114"/>
       <c r="I21" s="115">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J21" s="116">
-        <v>0</v>
-      </c>
-      <c r="K21" s="1">
+      <c r="J21" s="116"/>
+      <c r="K21" s="103">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -19824,7 +19560,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46206</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -19852,7 +19588,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46196</v>
+        <v>46205</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
@@ -19861,7 +19597,7 @@
     </row>
     <row r="6" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="230" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B6" s="230"/>
       <c r="C6" s="230"/>
@@ -20144,18 +19880,14 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G16" s="99"/>
-      <c r="H16" s="100">
-        <v>0</v>
-      </c>
+      <c r="H16" s="100"/>
       <c r="I16" s="101">
         <f>(G16*D16)*F16+H16*F16</f>
         <v>0</v>
       </c>
-      <c r="J16" s="102">
-        <v>0</v>
-      </c>
+      <c r="J16" s="102"/>
       <c r="K16" s="103">
-        <f>I16*$K$13</f>
+        <f>I16*3.5%</f>
         <v>0</v>
       </c>
       <c r="L16" s="104">
@@ -20208,18 +19940,14 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G17" s="113"/>
-      <c r="H17" s="114">
-        <v>0</v>
-      </c>
+      <c r="H17" s="114"/>
       <c r="I17" s="115">
         <f t="shared" ref="I17:I23" si="2">(G17*D17)*F17+H17*F17</f>
         <v>0</v>
       </c>
-      <c r="J17" s="116">
-        <v>0</v>
-      </c>
-      <c r="K17" s="1">
-        <f t="shared" ref="K17:K21" si="3">I17*$K$13</f>
+      <c r="J17" s="116"/>
+      <c r="K17" s="103">
+        <f t="shared" ref="K17:K21" si="3">I17*3.5%</f>
         <v>0</v>
       </c>
       <c r="L17" s="104">
@@ -20272,17 +20000,13 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G18" s="113"/>
-      <c r="H18" s="114">
-        <v>0</v>
-      </c>
+      <c r="H18" s="114"/>
       <c r="I18" s="115">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J18" s="116">
-        <v>0</v>
-      </c>
-      <c r="K18" s="1">
+      <c r="J18" s="116"/>
+      <c r="K18" s="103">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -20332,17 +20056,13 @@
         <v>72.64</v>
       </c>
       <c r="G19" s="113"/>
-      <c r="H19" s="114">
-        <v>0</v>
-      </c>
+      <c r="H19" s="114"/>
       <c r="I19" s="115">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J19" s="116">
-        <v>0</v>
-      </c>
-      <c r="K19" s="1">
+      <c r="J19" s="116"/>
+      <c r="K19" s="103">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -20392,17 +20112,13 @@
         <v>72.64</v>
       </c>
       <c r="G20" s="113"/>
-      <c r="H20" s="114">
-        <v>0</v>
-      </c>
+      <c r="H20" s="114"/>
       <c r="I20" s="115">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J20" s="116">
-        <v>0</v>
-      </c>
-      <c r="K20" s="1">
+      <c r="J20" s="116"/>
+      <c r="K20" s="103">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -20452,17 +20168,13 @@
         <v>72.64</v>
       </c>
       <c r="G21" s="113"/>
-      <c r="H21" s="114">
-        <v>0</v>
-      </c>
+      <c r="H21" s="114"/>
       <c r="I21" s="115">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J21" s="116">
-        <v>0</v>
-      </c>
-      <c r="K21" s="1">
+      <c r="J21" s="116"/>
+      <c r="K21" s="103">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -21065,7 +20777,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46206</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -21093,7 +20805,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46196</v>
+        <v>46205</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
@@ -21102,7 +20814,7 @@
     </row>
     <row r="6" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="230" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B6" s="230"/>
       <c r="C6" s="230"/>
@@ -21385,18 +21097,14 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G16" s="99"/>
-      <c r="H16" s="100">
-        <v>0</v>
-      </c>
+      <c r="H16" s="100"/>
       <c r="I16" s="101">
         <f>(G16*D16)*F16+H16*F16</f>
         <v>0</v>
       </c>
-      <c r="J16" s="102">
-        <v>0</v>
-      </c>
+      <c r="J16" s="102"/>
       <c r="K16" s="103">
-        <f>I16*$K$13</f>
+        <f>I16*3.5%</f>
         <v>0</v>
       </c>
       <c r="L16" s="104">
@@ -21449,18 +21157,14 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G17" s="113"/>
-      <c r="H17" s="114">
-        <v>0</v>
-      </c>
+      <c r="H17" s="114"/>
       <c r="I17" s="115">
         <f t="shared" ref="I17:I23" si="2">(G17*D17)*F17+H17*F17</f>
         <v>0</v>
       </c>
-      <c r="J17" s="116">
-        <v>0</v>
-      </c>
-      <c r="K17" s="1">
-        <f t="shared" ref="K17:K21" si="3">I17*$K$13</f>
+      <c r="J17" s="116"/>
+      <c r="K17" s="103">
+        <f t="shared" ref="K17:K21" si="3">I17*3.5%</f>
         <v>0</v>
       </c>
       <c r="L17" s="104">
@@ -21513,17 +21217,13 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G18" s="113"/>
-      <c r="H18" s="114">
-        <v>0</v>
-      </c>
+      <c r="H18" s="114"/>
       <c r="I18" s="115">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J18" s="116">
-        <v>0</v>
-      </c>
-      <c r="K18" s="1">
+      <c r="J18" s="116"/>
+      <c r="K18" s="103">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -21573,17 +21273,13 @@
         <v>72.64</v>
       </c>
       <c r="G19" s="113"/>
-      <c r="H19" s="114">
-        <v>0</v>
-      </c>
+      <c r="H19" s="114"/>
       <c r="I19" s="115">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J19" s="116">
-        <v>0</v>
-      </c>
-      <c r="K19" s="1">
+      <c r="J19" s="116"/>
+      <c r="K19" s="103">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -21633,17 +21329,13 @@
         <v>72.64</v>
       </c>
       <c r="G20" s="113"/>
-      <c r="H20" s="114">
-        <v>0</v>
-      </c>
+      <c r="H20" s="114"/>
       <c r="I20" s="115">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J20" s="116">
-        <v>0</v>
-      </c>
-      <c r="K20" s="1">
+      <c r="J20" s="116"/>
+      <c r="K20" s="103">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -21693,17 +21385,13 @@
         <v>72.64</v>
       </c>
       <c r="G21" s="113"/>
-      <c r="H21" s="114">
-        <v>0</v>
-      </c>
+      <c r="H21" s="114"/>
       <c r="I21" s="115">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J21" s="116">
-        <v>0</v>
-      </c>
-      <c r="K21" s="1">
+      <c r="J21" s="116"/>
+      <c r="K21" s="103">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -22306,7 +21994,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46206</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -22334,7 +22022,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46196</v>
+        <v>46205</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
@@ -22343,7 +22031,7 @@
     </row>
     <row r="6" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="230" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B6" s="230"/>
       <c r="C6" s="230"/>
@@ -22626,18 +22314,14 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G16" s="99"/>
-      <c r="H16" s="100">
-        <v>0</v>
-      </c>
+      <c r="H16" s="100"/>
       <c r="I16" s="101">
         <f>(G16*D16)*F16+H16*F16</f>
         <v>0</v>
       </c>
-      <c r="J16" s="102">
-        <v>0</v>
-      </c>
+      <c r="J16" s="102"/>
       <c r="K16" s="103">
-        <f>I16*$K$13</f>
+        <f>I16*3.5%</f>
         <v>0</v>
       </c>
       <c r="L16" s="104">
@@ -22690,18 +22374,14 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G17" s="113"/>
-      <c r="H17" s="114">
-        <v>0</v>
-      </c>
+      <c r="H17" s="114"/>
       <c r="I17" s="115">
         <f t="shared" ref="I17:I23" si="2">(G17*D17)*F17+H17*F17</f>
         <v>0</v>
       </c>
-      <c r="J17" s="116">
-        <v>0</v>
-      </c>
-      <c r="K17" s="1">
-        <f t="shared" ref="K17:K21" si="3">I17*$K$13</f>
+      <c r="J17" s="116"/>
+      <c r="K17" s="103">
+        <f t="shared" ref="K17:K21" si="3">I17*3.5%</f>
         <v>0</v>
       </c>
       <c r="L17" s="104">
@@ -22754,17 +22434,13 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G18" s="113"/>
-      <c r="H18" s="114">
-        <v>0</v>
-      </c>
+      <c r="H18" s="114"/>
       <c r="I18" s="115">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J18" s="116">
-        <v>0</v>
-      </c>
-      <c r="K18" s="1">
+      <c r="J18" s="116"/>
+      <c r="K18" s="103">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -22814,17 +22490,13 @@
         <v>72.64</v>
       </c>
       <c r="G19" s="113"/>
-      <c r="H19" s="114">
-        <v>0</v>
-      </c>
+      <c r="H19" s="114"/>
       <c r="I19" s="115">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J19" s="116">
-        <v>0</v>
-      </c>
-      <c r="K19" s="1">
+      <c r="J19" s="116"/>
+      <c r="K19" s="103">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -22874,17 +22546,13 @@
         <v>72.64</v>
       </c>
       <c r="G20" s="113"/>
-      <c r="H20" s="114">
-        <v>0</v>
-      </c>
+      <c r="H20" s="114"/>
       <c r="I20" s="115">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J20" s="116">
-        <v>0</v>
-      </c>
-      <c r="K20" s="1">
+      <c r="J20" s="116"/>
+      <c r="K20" s="103">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -22934,17 +22602,13 @@
         <v>72.64</v>
       </c>
       <c r="G21" s="113"/>
-      <c r="H21" s="114">
-        <v>0</v>
-      </c>
+      <c r="H21" s="114"/>
       <c r="I21" s="115">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J21" s="116">
-        <v>0</v>
-      </c>
-      <c r="K21" s="1">
+      <c r="J21" s="116"/>
+      <c r="K21" s="103">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -23552,7 +23216,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46206</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -23567,7 +23231,7 @@
     </row>
     <row r="5" spans="1:21 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="245" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B5" s="245"/>
       <c r="C5" s="245"/>
@@ -23580,7 +23244,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46196</v>
+        <v>46205</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
@@ -23670,7 +23334,7 @@
       <c r="A10" s="228"/>
       <c r="B10" s="75"/>
       <c r="C10" s="75" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F10" s="70"/>
       <c r="G10" s="71"/>
@@ -23726,7 +23390,7 @@
       <c r="R12" s="70"/>
       <c r="S12" s="71"/>
       <c r="T12" s="200" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="U12" s="201"/>
       <c r="XFD12" t="s">
@@ -23793,7 +23457,7 @@
       </c>
       <c r="U14" s="163">
         <f>+'1'!P35</f>
-        <v>49856.113638360002</v>
+        <v>11110.404923887503</v>
       </c>
       <c r="XFD14" t="s">
         <v>75</v>
@@ -23879,15 +23543,15 @@
       <c r="G16" s="113"/>
       <c r="H16" s="171">
         <f>+'1'!H16+'2'!H16+'4'!H16+'3'!H16+'5'!H16+'6'!H16+'7'!H16+'8'!H16+'9'!H16+'10'!H16+'11'!H16+'12'!H16+'13'!H16+'14'!H16+'15'!H16+'16'!H16+'17'!H16+'18'!H16</f>
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="I16" s="1">
         <f>(G16*D16)*F16+H16*F16</f>
-        <v>4406.8499999999995</v>
+        <v>0</v>
       </c>
       <c r="J16" s="171">
         <f>+'1'!J16+'2'!J16+'4'!J16+'3'!J16+'5'!J16+'6'!J16+'7'!J16+'8'!J16+'9'!J16+'10'!J16+'11'!J16+'12'!J16+'13'!J16+'14'!J16+'15'!J16+'16'!J16+'17'!J16+'18'!J16</f>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K16" s="171">
         <f>+'1'!K16+'2'!K16+'4'!K16+'3'!K16+'5'!K16+'6'!K16+'7'!K16+'8'!K16+'9'!K16+'10'!K16</f>
@@ -23895,23 +23559,23 @@
       </c>
       <c r="L16" s="174">
         <f>+'1'!L16+'2'!L16+'4'!L16+'3'!L16+'5'!L16+'6'!L16+'7'!L16+'8'!L16+'9'!L16+'10'!L16</f>
-        <v>616.95899999999995</v>
+        <v>0</v>
       </c>
       <c r="M16" s="105">
         <f>I16-K16-L16</f>
-        <v>3789.8909999999996</v>
+        <v>0</v>
       </c>
       <c r="N16" s="100">
         <f>+'1'!N16+'2'!N16+'4'!N16+'3'!N16+'5'!N16+'6'!N16+'7'!N16+'8'!N16+'9'!N16+'10'!N16</f>
-        <v>719.95337999999992</v>
+        <v>0</v>
       </c>
       <c r="O16" s="100">
         <f>+'1'!O16+'2'!O16+'4'!O16+'3'!O16+'5'!O16+'6'!O16+'7'!O16+'8'!O16+'9'!O16+'10'!O16</f>
-        <v>22.549221899999999</v>
+        <v>0</v>
       </c>
       <c r="P16" s="104">
         <f t="shared" ref="P16:P24" si="0">M16+N16+O16</f>
-        <v>4532.3936018999993</v>
+        <v>0</v>
       </c>
       <c r="Q16" s="107"/>
       <c r="T16" s="162" t="str">
@@ -23953,39 +23617,39 @@
       <c r="G17" s="113"/>
       <c r="H17" s="171">
         <f>+'1'!H17+'2'!H17+'4'!H17+'3'!H17+'5'!H17+'6'!H17+'7'!H17+'8'!H17+'9'!H17+'10'!H17+'11'!H17+'12'!H17+'13'!H17+'14'!H17+'15'!H17+'16'!H17+'17'!H17+'18'!H17</f>
-        <v>84</v>
+        <v>42</v>
       </c>
       <c r="I17" s="1">
         <f t="shared" ref="I17:I23" si="1">(G17*D17)*F17+H17*F17</f>
-        <v>4406.8499999999995</v>
+        <v>2203.4249999999997</v>
       </c>
       <c r="J17" s="171">
         <f>+'1'!J17+'2'!J17+'4'!J17+'3'!J17+'5'!J17+'6'!J17+'7'!J17+'8'!J17+'9'!J17+'10'!J17+'11'!J17+'12'!J17+'13'!J17+'14'!J17+'15'!J17+'16'!J17+'17'!J17+'18'!J17</f>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K17" s="171">
         <f>+'1'!K17+'2'!K17+'4'!K17+'3'!K17+'5'!K17+'6'!K17+'7'!K17+'8'!K17+'9'!K17+'10'!K17</f>
-        <v>0</v>
+        <v>77.119874999999993</v>
       </c>
       <c r="L17" s="174">
         <f>+'1'!L17+'2'!L17+'4'!L17+'3'!L17+'5'!L17+'6'!L17+'7'!L17+'8'!L17+'9'!L17+'10'!L17</f>
-        <v>616.95899999999995</v>
+        <v>308.47949999999997</v>
       </c>
       <c r="M17" s="117">
         <f t="shared" ref="M17:M23" si="2">I17-K17-L17</f>
-        <v>3789.8909999999996</v>
+        <v>1817.8256249999999</v>
       </c>
       <c r="N17" s="100">
         <f>+'1'!N17+'2'!N17+'4'!N17+'3'!N17+'5'!N17+'6'!N17+'7'!N17+'8'!N17+'9'!N17+'10'!N17</f>
-        <v>719.95337999999992</v>
+        <v>327.20861249999996</v>
       </c>
       <c r="O17" s="100">
         <f>+'1'!O17+'2'!O17+'4'!O17+'3'!O17+'5'!O17+'6'!O17+'7'!O17+'8'!O17+'9'!O17+'10'!O17</f>
-        <v>22.549221899999999</v>
+        <v>10.725171187500001</v>
       </c>
       <c r="P17" s="119">
         <f t="shared" si="0"/>
-        <v>4532.3936018999993</v>
+        <v>2155.7594086875001</v>
       </c>
       <c r="S17" s="64"/>
       <c r="T17" s="162" t="str">
@@ -24097,39 +23761,39 @@
       <c r="G19" s="113"/>
       <c r="H19" s="171">
         <f>+'1'!H19+'2'!H19+'4'!H19+'3'!H19+'5'!H19+'6'!H19+'7'!H19+'8'!H19+'9'!H19+'10'!H19+'11'!H19+'12'!H19+'13'!H19+'14'!H19+'15'!H19+'16'!H19+'17'!H19+'18'!H19</f>
-        <v>168</v>
+        <v>42</v>
       </c>
       <c r="I19" s="1">
         <f t="shared" si="1"/>
-        <v>12203.52</v>
+        <v>3050.88</v>
       </c>
       <c r="J19" s="171">
         <f>+'1'!J19+'2'!J19+'4'!J19+'3'!J19+'5'!J19+'6'!J19+'7'!J19+'8'!J19+'9'!J19+'10'!J19+'11'!J19+'12'!J19+'13'!J19+'14'!J19+'15'!J19+'16'!J19+'17'!J19+'18'!J19</f>
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K19" s="171">
         <f>+'1'!K19+'2'!K19+'4'!K19+'3'!K19+'5'!K19+'6'!K19+'7'!K19+'8'!K19+'9'!K19+'10'!K19</f>
-        <v>0</v>
+        <v>106.78080000000001</v>
       </c>
       <c r="L19" s="174">
         <f>+'1'!L19+'2'!L19+'4'!L19+'3'!L19+'5'!L19+'6'!L19+'7'!L19+'8'!L19+'9'!L19+'10'!L19</f>
-        <v>1708.4928000000002</v>
+        <v>427.12320000000005</v>
       </c>
       <c r="M19" s="117">
         <f t="shared" si="2"/>
-        <v>10495.0272</v>
+        <v>2516.9760000000001</v>
       </c>
       <c r="N19" s="100">
         <f>+'1'!N19+'2'!N19+'4'!N19+'3'!N19+'5'!N19+'6'!N19+'7'!N19+'8'!N19+'9'!N19+'10'!N19</f>
-        <v>1993.706496</v>
+        <v>453.05568</v>
       </c>
       <c r="O19" s="100">
         <f>+'1'!O19+'2'!O19+'4'!O19+'3'!O19+'5'!O19+'6'!O19+'7'!O19+'8'!O19+'9'!O19+'10'!O19</f>
-        <v>62.443668480000007</v>
+        <v>14.8501584</v>
       </c>
       <c r="P19" s="119">
         <f t="shared" si="0"/>
-        <v>12551.177364480001</v>
+        <v>2984.8818384000001</v>
       </c>
       <c r="T19" s="162" t="str">
         <f>+'6'!A5</f>
@@ -24167,39 +23831,39 @@
       <c r="G20" s="113"/>
       <c r="H20" s="171">
         <f>+'1'!H20+'2'!H20+'4'!H20+'3'!H20+'5'!H20+'6'!H20+'7'!H20+'8'!H20+'9'!H20+'10'!H20+'11'!H20+'12'!H20+'13'!H20+'14'!H20+'15'!H20+'16'!H20+'17'!H20+'18'!H20</f>
-        <v>126</v>
+        <v>42</v>
       </c>
       <c r="I20" s="1">
         <f t="shared" si="1"/>
-        <v>9152.64</v>
+        <v>3050.88</v>
       </c>
       <c r="J20" s="171">
         <f>+'1'!J20+'2'!J20+'4'!J20+'3'!J20+'5'!J20+'6'!J20+'7'!J20+'8'!J20+'9'!J20+'10'!J20+'11'!J20+'12'!J20+'13'!J20+'14'!J20+'15'!J20+'16'!J20+'17'!J20+'18'!J20</f>
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K20" s="171">
         <f>+'1'!K20+'2'!K20+'4'!K20+'3'!K20+'5'!K20+'6'!K20+'7'!K20+'8'!K20+'9'!K20+'10'!K20</f>
-        <v>0</v>
+        <v>106.78080000000001</v>
       </c>
       <c r="L20" s="174">
         <f>+'1'!L20+'2'!L20+'4'!L20+'3'!L20+'5'!L20+'6'!L20+'7'!L20+'8'!L20+'9'!L20+'10'!L20</f>
-        <v>1281.3696</v>
+        <v>427.12320000000005</v>
       </c>
       <c r="M20" s="117">
         <f t="shared" si="2"/>
-        <v>7871.2703999999994</v>
+        <v>2516.9760000000001</v>
       </c>
       <c r="N20" s="100">
         <f>+'1'!N20+'2'!N20+'4'!N20+'3'!N20+'5'!N20+'6'!N20+'7'!N20+'8'!N20+'9'!N20+'10'!N20</f>
-        <v>1495.2798719999998</v>
+        <v>453.05568</v>
       </c>
       <c r="O20" s="100">
         <f>+'1'!O20+'2'!O20+'4'!O20+'3'!O20+'5'!O20+'6'!O20+'7'!O20+'8'!O20+'9'!O20+'10'!O20</f>
-        <v>46.832751359999996</v>
+        <v>14.8501584</v>
       </c>
       <c r="P20" s="119">
         <f t="shared" si="0"/>
-        <v>9413.3830233599983</v>
+        <v>2984.8818384000001</v>
       </c>
       <c r="T20" s="162" t="str">
         <f>+'7'!A5</f>
@@ -24237,39 +23901,39 @@
       <c r="G21" s="113"/>
       <c r="H21" s="171">
         <f>+'1'!H21+'2'!H21+'4'!H21+'3'!H21+'5'!H21+'6'!H21+'7'!H21+'8'!H21+'9'!H21+'10'!H21+'11'!H21+'12'!H21+'13'!H21+'14'!H21+'15'!H21+'16'!H21+'17'!H21+'18'!H21</f>
-        <v>252</v>
+        <v>42</v>
       </c>
       <c r="I21" s="1">
         <f t="shared" si="1"/>
-        <v>18305.28</v>
+        <v>3050.88</v>
       </c>
       <c r="J21" s="171">
         <f>+'1'!J21+'2'!J21+'4'!J21+'3'!J21+'5'!J21+'6'!J21+'7'!J21+'8'!J21+'9'!J21+'10'!J21+'11'!J21+'12'!J21+'13'!J21+'14'!J21+'15'!J21+'16'!J21+'17'!J21+'18'!J21</f>
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K21" s="171">
         <f>+'1'!K21+'2'!K21+'4'!K21+'3'!K21+'5'!K21+'6'!K21+'7'!K21+'8'!K21+'9'!K21+'10'!K21</f>
-        <v>0</v>
+        <v>106.78080000000001</v>
       </c>
       <c r="L21" s="174">
         <f>+'1'!L21+'2'!L21+'4'!L21+'3'!L21+'5'!L21+'6'!L21+'7'!L21+'8'!L21+'9'!L21+'10'!L21</f>
-        <v>2562.7392</v>
+        <v>427.12320000000005</v>
       </c>
       <c r="M21" s="117">
         <f t="shared" si="2"/>
-        <v>15742.540799999999</v>
+        <v>2516.9760000000001</v>
       </c>
       <c r="N21" s="100">
         <f>+'1'!N21+'2'!N21+'4'!N21+'3'!N21+'5'!N21+'6'!N21+'7'!N21+'8'!N21+'9'!N21+'10'!N21</f>
-        <v>2990.5597439999997</v>
+        <v>453.05568</v>
       </c>
       <c r="O21" s="100">
         <f>+'1'!O21+'2'!O21+'4'!O21+'3'!O21+'5'!O21+'6'!O21+'7'!O21+'8'!O21+'9'!O21+'10'!O21</f>
-        <v>93.665502719999992</v>
+        <v>14.8501584</v>
       </c>
       <c r="P21" s="119">
         <f t="shared" si="0"/>
-        <v>18826.766046719997</v>
+        <v>2984.8818384000001</v>
       </c>
       <c r="T21" s="162" t="str">
         <f>+'8'!A5</f>
@@ -24497,7 +24161,7 @@
       <c r="B25" s="211"/>
       <c r="C25" s="212">
         <f>H25/40</f>
-        <v>17.850000000000001</v>
+        <v>4.2</v>
       </c>
       <c r="D25" s="206"/>
       <c r="E25" s="206"/>
@@ -24508,39 +24172,39 @@
       </c>
       <c r="H25" s="176">
         <f t="shared" si="3"/>
-        <v>714</v>
+        <v>168</v>
       </c>
       <c r="I25" s="177">
         <f t="shared" si="3"/>
-        <v>48475.14</v>
+        <v>11356.065000000002</v>
       </c>
       <c r="J25" s="176">
         <f t="shared" si="3"/>
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="K25" s="177">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>397.46227500000003</v>
       </c>
       <c r="L25" s="178">
         <f t="shared" si="3"/>
-        <v>6786.5195999999996</v>
+        <v>1589.8491000000001</v>
       </c>
       <c r="M25" s="140">
         <f t="shared" si="3"/>
-        <v>41688.6204</v>
+        <v>9368.7536250000012</v>
       </c>
       <c r="N25" s="141">
         <f>SUM(N16:N24)</f>
-        <v>7919.4528719999998</v>
+        <v>1686.3756524999999</v>
       </c>
       <c r="O25" s="142">
         <f>SUM(O16:O24)</f>
-        <v>248.04036636000001</v>
+        <v>55.275646387499997</v>
       </c>
       <c r="P25" s="143">
         <f>SUM(P16:P24)</f>
-        <v>49856.113638359995</v>
+        <v>11110.404923887501</v>
       </c>
       <c r="T25" s="162" t="str">
         <f>+'12'!A5</f>
@@ -24748,7 +24412,7 @@
       </c>
       <c r="U33" s="164">
         <f>SUM(U14:U28)</f>
-        <v>49856.113638360002</v>
+        <v>11110.404923887503</v>
       </c>
     </row>
     <row r="34" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -24781,7 +24445,7 @@
       <c r="O35" s="223"/>
       <c r="P35" s="151">
         <f>I25</f>
-        <v>48475.14</v>
+        <v>11356.065000000002</v>
       </c>
     </row>
     <row r="36" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -24802,7 +24466,7 @@
       <c r="O36" s="225"/>
       <c r="P36" s="152">
         <f>L25</f>
-        <v>6786.5195999999996</v>
+        <v>1589.8491000000001</v>
       </c>
     </row>
     <row r="37" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -24823,7 +24487,7 @@
       <c r="O37" s="225"/>
       <c r="P37" s="153">
         <f>K25</f>
-        <v>0</v>
+        <v>397.46227500000003</v>
       </c>
     </row>
     <row r="38" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -24845,7 +24509,7 @@
       <c r="O38" s="225"/>
       <c r="P38" s="152">
         <f>P35-P36-P37</f>
-        <v>41688.6204</v>
+        <v>9368.753625000003</v>
       </c>
     </row>
     <row r="39" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -24870,7 +24534,7 @@
       </c>
       <c r="P39" s="152">
         <f>N25</f>
-        <v>7919.4528719999998</v>
+        <v>1686.3756524999999</v>
       </c>
     </row>
     <row r="40" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -24892,7 +24556,7 @@
       <c r="O40" s="227"/>
       <c r="P40" s="152">
         <f>P38+P39</f>
-        <v>49608.073272000001</v>
+        <v>11055.129277500004</v>
       </c>
     </row>
     <row r="41" spans="1:21" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -24917,7 +24581,7 @@
       </c>
       <c r="P41" s="152">
         <f>O41*P40</f>
-        <v>1240.2018318</v>
+        <v>276.37823193750012</v>
       </c>
     </row>
     <row r="42" spans="1:21" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -24927,7 +24591,7 @@
       <c r="O42" s="205"/>
       <c r="P42" s="159">
         <f>P40+P41</f>
-        <v>50848.275103799999</v>
+        <v>11331.507509437504</v>
       </c>
     </row>
     <row r="43" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -25099,7 +24763,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46206</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -25127,7 +24791,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46196</v>
+        <v>46205</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
@@ -25136,7 +24800,7 @@
     </row>
     <row r="6" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="230" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B6" s="230"/>
       <c r="C6" s="230"/>
@@ -25294,7 +24958,9 @@
     </row>
     <row r="13" spans="1:19 16383:16384" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A13" s="229"/>
-      <c r="B13" s="167"/>
+      <c r="B13" s="75" t="s">
+        <v>102</v>
+      </c>
       <c r="J13" s="78"/>
       <c r="K13" s="78"/>
       <c r="L13" s="79">
@@ -25419,39 +25085,35 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G16" s="99"/>
-      <c r="H16" s="100">
-        <v>84</v>
-      </c>
+      <c r="H16" s="100"/>
       <c r="I16" s="101">
         <f>(G16*D16)*F16+H16*F16</f>
-        <v>4406.8499999999995</v>
-      </c>
-      <c r="J16" s="102">
-        <v>4</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J16" s="102"/>
       <c r="K16" s="103">
-        <f>I16*$K$13</f>
+        <f>I16*3.5%</f>
         <v>0</v>
       </c>
       <c r="L16" s="104">
         <f>I16*14%</f>
-        <v>616.95899999999995</v>
+        <v>0</v>
       </c>
       <c r="M16" s="105">
         <f>I16-K16-L16</f>
-        <v>3789.8909999999996</v>
+        <v>0</v>
       </c>
       <c r="N16" s="105">
         <f t="shared" ref="N16:N24" si="0">(M16*$N$15)+(J16*F16)*$N$15</f>
-        <v>719.95337999999992</v>
+        <v>0</v>
       </c>
       <c r="O16" s="106">
         <f t="shared" ref="O16:O24" si="1">(N16+M16)*$O$15</f>
-        <v>22.549221899999999</v>
+        <v>0</v>
       </c>
       <c r="P16" s="104">
         <f t="shared" ref="P16:P24" si="2">M16+N16+O16</f>
-        <v>4532.3936018999993</v>
+        <v>0</v>
       </c>
       <c r="Q16" s="107"/>
       <c r="XFD16" t="s">
@@ -25484,38 +25146,36 @@
       </c>
       <c r="G17" s="113"/>
       <c r="H17" s="114">
-        <v>84</v>
+        <v>42</v>
       </c>
       <c r="I17" s="115">
         <f t="shared" ref="I17:I23" si="3">(G17*D17)*F17+H17*F17</f>
-        <v>4406.8499999999995</v>
-      </c>
-      <c r="J17" s="116">
-        <v>4</v>
-      </c>
-      <c r="K17" s="1">
-        <f t="shared" ref="K17:K21" si="4">I17*$K$13</f>
-        <v>0</v>
+        <v>2203.4249999999997</v>
+      </c>
+      <c r="J17" s="116"/>
+      <c r="K17" s="103">
+        <f t="shared" ref="K17:K21" si="4">I17*3.5%</f>
+        <v>77.119874999999993</v>
       </c>
       <c r="L17" s="104">
         <f t="shared" ref="L17:L21" si="5">I17*14%</f>
-        <v>616.95899999999995</v>
+        <v>308.47949999999997</v>
       </c>
       <c r="M17" s="117">
         <f t="shared" ref="M17:M23" si="6">I17-K17-L17</f>
-        <v>3789.8909999999996</v>
+        <v>1817.8256249999999</v>
       </c>
       <c r="N17" s="117">
         <f t="shared" si="0"/>
-        <v>719.95337999999992</v>
+        <v>327.20861249999996</v>
       </c>
       <c r="O17" s="118">
         <f t="shared" si="1"/>
-        <v>22.549221899999999</v>
+        <v>10.725171187500001</v>
       </c>
       <c r="P17" s="119">
         <f t="shared" si="2"/>
-        <v>4532.3936018999993</v>
+        <v>2155.7594086875001</v>
       </c>
       <c r="S17" s="64"/>
       <c r="XFD17" t="s">
@@ -25547,17 +25207,13 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G18" s="113"/>
-      <c r="H18" s="114">
-        <v>0</v>
-      </c>
+      <c r="H18" s="114"/>
       <c r="I18" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J18" s="116">
-        <v>0</v>
-      </c>
-      <c r="K18" s="1">
+      <c r="J18" s="116"/>
+      <c r="K18" s="103">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -25608,38 +25264,36 @@
       </c>
       <c r="G19" s="113"/>
       <c r="H19" s="114">
-        <v>168</v>
+        <v>42</v>
       </c>
       <c r="I19" s="115">
         <f t="shared" si="3"/>
-        <v>12203.52</v>
-      </c>
-      <c r="J19" s="116">
-        <v>8</v>
-      </c>
-      <c r="K19" s="1">
+        <v>3050.88</v>
+      </c>
+      <c r="J19" s="116"/>
+      <c r="K19" s="103">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>106.78080000000001</v>
       </c>
       <c r="L19" s="104">
         <f t="shared" si="5"/>
-        <v>1708.4928000000002</v>
+        <v>427.12320000000005</v>
       </c>
       <c r="M19" s="117">
         <f t="shared" si="6"/>
-        <v>10495.0272</v>
+        <v>2516.9760000000001</v>
       </c>
       <c r="N19" s="117">
         <f t="shared" si="0"/>
-        <v>1993.706496</v>
+        <v>453.05568</v>
       </c>
       <c r="O19" s="118">
         <f t="shared" si="1"/>
-        <v>62.443668480000007</v>
+        <v>14.8501584</v>
       </c>
       <c r="P19" s="119">
         <f t="shared" si="2"/>
-        <v>12551.177364480001</v>
+        <v>2984.8818384000001</v>
       </c>
     </row>
     <row r="20" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -25668,38 +25322,36 @@
       </c>
       <c r="G20" s="113"/>
       <c r="H20" s="114">
-        <v>126</v>
+        <v>42</v>
       </c>
       <c r="I20" s="115">
         <f t="shared" si="3"/>
-        <v>9152.64</v>
-      </c>
-      <c r="J20" s="116">
-        <v>6</v>
-      </c>
-      <c r="K20" s="1">
+        <v>3050.88</v>
+      </c>
+      <c r="J20" s="116"/>
+      <c r="K20" s="103">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>106.78080000000001</v>
       </c>
       <c r="L20" s="104">
         <f t="shared" si="5"/>
-        <v>1281.3696</v>
+        <v>427.12320000000005</v>
       </c>
       <c r="M20" s="117">
         <f t="shared" si="6"/>
-        <v>7871.2703999999994</v>
+        <v>2516.9760000000001</v>
       </c>
       <c r="N20" s="117">
         <f t="shared" si="0"/>
-        <v>1495.2798719999998</v>
+        <v>453.05568</v>
       </c>
       <c r="O20" s="118">
         <f t="shared" si="1"/>
-        <v>46.832751359999996</v>
+        <v>14.8501584</v>
       </c>
       <c r="P20" s="119">
         <f t="shared" si="2"/>
-        <v>9413.3830233599983</v>
+        <v>2984.8818384000001</v>
       </c>
     </row>
     <row r="21" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -25728,38 +25380,36 @@
       </c>
       <c r="G21" s="113"/>
       <c r="H21" s="114">
-        <v>252</v>
+        <v>42</v>
       </c>
       <c r="I21" s="115">
         <f t="shared" si="3"/>
-        <v>18305.28</v>
-      </c>
-      <c r="J21" s="116">
-        <v>12</v>
-      </c>
-      <c r="K21" s="1">
+        <v>3050.88</v>
+      </c>
+      <c r="J21" s="116"/>
+      <c r="K21" s="103">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>106.78080000000001</v>
       </c>
       <c r="L21" s="104">
         <f t="shared" si="5"/>
-        <v>2562.7392</v>
+        <v>427.12320000000005</v>
       </c>
       <c r="M21" s="117">
         <f t="shared" si="6"/>
-        <v>15742.540799999999</v>
+        <v>2516.9760000000001</v>
       </c>
       <c r="N21" s="117">
         <f t="shared" si="0"/>
-        <v>2990.5597439999997</v>
+        <v>453.05568</v>
       </c>
       <c r="O21" s="118">
         <f t="shared" si="1"/>
-        <v>93.665502719999992</v>
+        <v>14.8501584</v>
       </c>
       <c r="P21" s="119">
         <f t="shared" si="2"/>
-        <v>18826.766046719997</v>
+        <v>2984.8818384000001</v>
       </c>
     </row>
     <row r="22" spans="1:19 16384:16384" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -25945,39 +25595,39 @@
       </c>
       <c r="H25" s="135">
         <f t="shared" si="9"/>
-        <v>714</v>
+        <v>168</v>
       </c>
       <c r="I25" s="136">
         <f t="shared" si="9"/>
-        <v>48475.14</v>
+        <v>11356.065000000002</v>
       </c>
       <c r="J25" s="182">
         <f>SUM(J16:J21)</f>
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="K25" s="138">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>397.46227500000003</v>
       </c>
       <c r="L25" s="139">
         <f t="shared" si="9"/>
-        <v>6786.5195999999996</v>
+        <v>1589.8491000000001</v>
       </c>
       <c r="M25" s="140">
         <f t="shared" si="9"/>
-        <v>41688.6204</v>
+        <v>9368.7536250000012</v>
       </c>
       <c r="N25" s="141">
         <f>SUM(N16:N24)</f>
-        <v>7919.4528719999998</v>
+        <v>1686.3756524999999</v>
       </c>
       <c r="O25" s="142">
         <f>SUM(O16:O24)</f>
-        <v>248.04036636000001</v>
+        <v>55.275646387499997</v>
       </c>
       <c r="P25" s="143">
         <f>SUM(P16:P24)</f>
-        <v>49856.113638359995</v>
+        <v>11110.404923887501</v>
       </c>
     </row>
     <row r="26" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -26027,7 +25677,7 @@
       <c r="O28" s="223"/>
       <c r="P28" s="151">
         <f>I25</f>
-        <v>48475.14</v>
+        <v>11356.065000000002</v>
       </c>
     </row>
     <row r="29" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -26048,7 +25698,7 @@
       <c r="O29" s="225"/>
       <c r="P29" s="152">
         <f>L25</f>
-        <v>6786.5195999999996</v>
+        <v>1589.8491000000001</v>
       </c>
     </row>
     <row r="30" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -26069,7 +25719,7 @@
       <c r="O30" s="225"/>
       <c r="P30" s="153">
         <f>K25</f>
-        <v>0</v>
+        <v>397.46227500000003</v>
       </c>
     </row>
     <row r="31" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -26091,7 +25741,7 @@
       <c r="O31" s="225"/>
       <c r="P31" s="152">
         <f>P28-P29-P30</f>
-        <v>41688.6204</v>
+        <v>9368.753625000003</v>
       </c>
     </row>
     <row r="32" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -26116,7 +25766,7 @@
       </c>
       <c r="P32" s="152">
         <f>N25</f>
-        <v>7919.4528719999998</v>
+        <v>1686.3756524999999</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -26138,7 +25788,7 @@
       <c r="O33" s="227"/>
       <c r="P33" s="152">
         <f>P31+P32</f>
-        <v>49608.073272000001</v>
+        <v>11055.129277500004</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -26163,7 +25813,7 @@
       </c>
       <c r="P34" s="152">
         <f>O34*P33</f>
-        <v>248.04036636000001</v>
+        <v>55.275646387500018</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -26173,7 +25823,7 @@
       <c r="O35" s="205"/>
       <c r="P35" s="159">
         <f>P33+P34</f>
-        <v>49856.113638360002</v>
+        <v>11110.404923887503</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -26345,7 +25995,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46206</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -26373,7 +26023,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46196</v>
+        <v>46205</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
@@ -26382,7 +26032,7 @@
     </row>
     <row r="6" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="230" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B6" s="230"/>
       <c r="C6" s="230"/>
@@ -26665,18 +26315,14 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G16" s="99"/>
-      <c r="H16" s="100">
-        <v>0</v>
-      </c>
+      <c r="H16" s="100"/>
       <c r="I16" s="101">
         <f>(G16*D16)*F16+H16*F16</f>
         <v>0</v>
       </c>
-      <c r="J16" s="102">
-        <v>0</v>
-      </c>
+      <c r="J16" s="102"/>
       <c r="K16" s="103">
-        <f>I16*$K$13</f>
+        <f>I16*3.5%</f>
         <v>0</v>
       </c>
       <c r="L16" s="104">
@@ -26729,18 +26375,14 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G17" s="113"/>
-      <c r="H17" s="114">
-        <v>0</v>
-      </c>
+      <c r="H17" s="114"/>
       <c r="I17" s="115">
         <f t="shared" ref="I17:I23" si="2">(G17*D17)*F17+H17*F17</f>
         <v>0</v>
       </c>
-      <c r="J17" s="116">
-        <v>0</v>
-      </c>
-      <c r="K17" s="1">
-        <f t="shared" ref="K17:K21" si="3">I17*$K$13</f>
+      <c r="J17" s="116"/>
+      <c r="K17" s="103">
+        <f t="shared" ref="K17:K21" si="3">I17*3.5%</f>
         <v>0</v>
       </c>
       <c r="L17" s="104">
@@ -26793,17 +26435,13 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G18" s="113"/>
-      <c r="H18" s="114">
-        <v>0</v>
-      </c>
+      <c r="H18" s="114"/>
       <c r="I18" s="115">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J18" s="116">
-        <v>0</v>
-      </c>
-      <c r="K18" s="1">
+      <c r="J18" s="116"/>
+      <c r="K18" s="103">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -26853,17 +26491,13 @@
         <v>72.64</v>
       </c>
       <c r="G19" s="113"/>
-      <c r="H19" s="114">
-        <v>0</v>
-      </c>
+      <c r="H19" s="114"/>
       <c r="I19" s="115">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J19" s="116">
-        <v>0</v>
-      </c>
-      <c r="K19" s="1">
+      <c r="J19" s="116"/>
+      <c r="K19" s="103">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -26913,17 +26547,13 @@
         <v>72.64</v>
       </c>
       <c r="G20" s="113"/>
-      <c r="H20" s="114">
-        <v>0</v>
-      </c>
+      <c r="H20" s="114"/>
       <c r="I20" s="115">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J20" s="116">
-        <v>0</v>
-      </c>
-      <c r="K20" s="1">
+      <c r="J20" s="116"/>
+      <c r="K20" s="103">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -26973,17 +26603,13 @@
         <v>72.64</v>
       </c>
       <c r="G21" s="113"/>
-      <c r="H21" s="114">
-        <v>0</v>
-      </c>
+      <c r="H21" s="114"/>
       <c r="I21" s="115">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J21" s="116">
-        <v>0</v>
-      </c>
-      <c r="K21" s="1">
+      <c r="J21" s="116"/>
+      <c r="K21" s="103">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -27590,7 +27216,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46206</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -27618,7 +27244,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46196</v>
+        <v>46205</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
@@ -27627,7 +27253,7 @@
     </row>
     <row r="6" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="230" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B6" s="230"/>
       <c r="C6" s="230"/>
@@ -27910,18 +27536,14 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G16" s="99"/>
-      <c r="H16" s="100">
-        <v>0</v>
-      </c>
+      <c r="H16" s="100"/>
       <c r="I16" s="101">
         <f>(G16*D16)*F16+H16*F16</f>
         <v>0</v>
       </c>
-      <c r="J16" s="102">
-        <v>0</v>
-      </c>
+      <c r="J16" s="102"/>
       <c r="K16" s="103">
-        <f>I16*$K$13</f>
+        <f>I16*3.5%</f>
         <v>0</v>
       </c>
       <c r="L16" s="104">
@@ -27974,18 +27596,14 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G17" s="113"/>
-      <c r="H17" s="114">
-        <v>0</v>
-      </c>
+      <c r="H17" s="114"/>
       <c r="I17" s="115">
         <f t="shared" ref="I17:I23" si="2">(G17*D17)*F17+H17*F17</f>
         <v>0</v>
       </c>
-      <c r="J17" s="116">
-        <v>0</v>
-      </c>
-      <c r="K17" s="1">
-        <f t="shared" ref="K17:K21" si="3">I17*$K$13</f>
+      <c r="J17" s="116"/>
+      <c r="K17" s="103">
+        <f t="shared" ref="K17:K21" si="3">I17*3.5%</f>
         <v>0</v>
       </c>
       <c r="L17" s="104">
@@ -28038,17 +27656,13 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G18" s="113"/>
-      <c r="H18" s="114">
-        <v>0</v>
-      </c>
+      <c r="H18" s="114"/>
       <c r="I18" s="115">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J18" s="116">
-        <v>0</v>
-      </c>
-      <c r="K18" s="1">
+      <c r="J18" s="116"/>
+      <c r="K18" s="103">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -28098,17 +27712,13 @@
         <v>72.64</v>
       </c>
       <c r="G19" s="113"/>
-      <c r="H19" s="114">
-        <v>0</v>
-      </c>
+      <c r="H19" s="114"/>
       <c r="I19" s="115">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J19" s="116">
-        <v>0</v>
-      </c>
-      <c r="K19" s="1">
+      <c r="J19" s="116"/>
+      <c r="K19" s="103">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -28158,17 +27768,13 @@
         <v>72.64</v>
       </c>
       <c r="G20" s="113"/>
-      <c r="H20" s="114">
-        <v>0</v>
-      </c>
+      <c r="H20" s="114"/>
       <c r="I20" s="115">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J20" s="116">
-        <v>0</v>
-      </c>
-      <c r="K20" s="1">
+      <c r="J20" s="116"/>
+      <c r="K20" s="103">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -28218,17 +27824,13 @@
         <v>72.64</v>
       </c>
       <c r="G21" s="113"/>
-      <c r="H21" s="114">
-        <v>0</v>
-      </c>
+      <c r="H21" s="114"/>
       <c r="I21" s="115">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J21" s="116">
-        <v>0</v>
-      </c>
-      <c r="K21" s="1">
+      <c r="J21" s="116"/>
+      <c r="K21" s="103">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -28834,7 +28436,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46206</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -28862,7 +28464,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46196</v>
+        <v>46205</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
@@ -28871,7 +28473,7 @@
     </row>
     <row r="6" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="230" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B6" s="230"/>
       <c r="C6" s="230"/>
@@ -29154,18 +28756,14 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G16" s="99"/>
-      <c r="H16" s="100">
-        <v>0</v>
-      </c>
+      <c r="H16" s="100"/>
       <c r="I16" s="101">
         <f>(G16*D16)*F16+H16*F16</f>
         <v>0</v>
       </c>
-      <c r="J16" s="102">
-        <v>0</v>
-      </c>
+      <c r="J16" s="102"/>
       <c r="K16" s="103">
-        <f>I16*$K$13</f>
+        <f>I16*3.5%</f>
         <v>0</v>
       </c>
       <c r="L16" s="104">
@@ -29218,18 +28816,14 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G17" s="113"/>
-      <c r="H17" s="114">
-        <v>0</v>
-      </c>
+      <c r="H17" s="114"/>
       <c r="I17" s="115">
         <f t="shared" ref="I17:I23" si="2">(G17*D17)*F17+H17*F17</f>
         <v>0</v>
       </c>
-      <c r="J17" s="116">
-        <v>0</v>
-      </c>
-      <c r="K17" s="1">
-        <f t="shared" ref="K17:K21" si="3">I17*$K$13</f>
+      <c r="J17" s="116"/>
+      <c r="K17" s="103">
+        <f t="shared" ref="K17:K21" si="3">I17*3.5%</f>
         <v>0</v>
       </c>
       <c r="L17" s="104">
@@ -29282,17 +28876,13 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G18" s="113"/>
-      <c r="H18" s="114">
-        <v>0</v>
-      </c>
+      <c r="H18" s="114"/>
       <c r="I18" s="115">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J18" s="116">
-        <v>0</v>
-      </c>
-      <c r="K18" s="1">
+      <c r="J18" s="116"/>
+      <c r="K18" s="103">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -29342,17 +28932,13 @@
         <v>72.64</v>
       </c>
       <c r="G19" s="113"/>
-      <c r="H19" s="114">
-        <v>0</v>
-      </c>
+      <c r="H19" s="114"/>
       <c r="I19" s="115">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J19" s="116">
-        <v>0</v>
-      </c>
-      <c r="K19" s="1">
+      <c r="J19" s="116"/>
+      <c r="K19" s="103">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -29402,17 +28988,13 @@
         <v>72.64</v>
       </c>
       <c r="G20" s="113"/>
-      <c r="H20" s="114">
-        <v>0</v>
-      </c>
+      <c r="H20" s="114"/>
       <c r="I20" s="115">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J20" s="116">
-        <v>0</v>
-      </c>
-      <c r="K20" s="1">
+      <c r="J20" s="116"/>
+      <c r="K20" s="103">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -29462,17 +29044,13 @@
         <v>72.64</v>
       </c>
       <c r="G21" s="113"/>
-      <c r="H21" s="114">
-        <v>0</v>
-      </c>
+      <c r="H21" s="114"/>
       <c r="I21" s="115">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J21" s="116">
-        <v>0</v>
-      </c>
-      <c r="K21" s="1">
+      <c r="J21" s="116"/>
+      <c r="K21" s="103">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -30079,7 +29657,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46206</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -30107,7 +29685,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46196</v>
+        <v>46205</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
@@ -30116,7 +29694,7 @@
     </row>
     <row r="6" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="230" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B6" s="230"/>
       <c r="C6" s="230"/>
@@ -30399,18 +29977,14 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G16" s="99"/>
-      <c r="H16" s="100">
-        <v>0</v>
-      </c>
+      <c r="H16" s="100"/>
       <c r="I16" s="101">
         <f>(G16*D16)*F16+H16*F16</f>
         <v>0</v>
       </c>
-      <c r="J16" s="102">
-        <v>0</v>
-      </c>
+      <c r="J16" s="102"/>
       <c r="K16" s="103">
-        <f>I16*$K$13</f>
+        <f>I16*3.5%</f>
         <v>0</v>
       </c>
       <c r="L16" s="104">
@@ -30463,18 +30037,14 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G17" s="113"/>
-      <c r="H17" s="114">
-        <v>0</v>
-      </c>
+      <c r="H17" s="114"/>
       <c r="I17" s="115">
         <f t="shared" ref="I17:I23" si="2">(G17*D17)*F17+H17*F17</f>
         <v>0</v>
       </c>
-      <c r="J17" s="116">
-        <v>0</v>
-      </c>
-      <c r="K17" s="1">
-        <f t="shared" ref="K17:K21" si="3">I17*$K$13</f>
+      <c r="J17" s="116"/>
+      <c r="K17" s="103">
+        <f t="shared" ref="K17:K21" si="3">I17*3.5%</f>
         <v>0</v>
       </c>
       <c r="L17" s="104">
@@ -30527,17 +30097,13 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G18" s="113"/>
-      <c r="H18" s="114">
-        <v>0</v>
-      </c>
+      <c r="H18" s="114"/>
       <c r="I18" s="115">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J18" s="116">
-        <v>0</v>
-      </c>
-      <c r="K18" s="1">
+      <c r="J18" s="116"/>
+      <c r="K18" s="103">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -30587,17 +30153,13 @@
         <v>72.64</v>
       </c>
       <c r="G19" s="113"/>
-      <c r="H19" s="114">
-        <v>0</v>
-      </c>
+      <c r="H19" s="114"/>
       <c r="I19" s="115">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J19" s="116">
-        <v>0</v>
-      </c>
-      <c r="K19" s="1">
+      <c r="J19" s="116"/>
+      <c r="K19" s="103">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -30647,17 +30209,13 @@
         <v>72.64</v>
       </c>
       <c r="G20" s="113"/>
-      <c r="H20" s="114">
-        <v>0</v>
-      </c>
+      <c r="H20" s="114"/>
       <c r="I20" s="115">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J20" s="116">
-        <v>0</v>
-      </c>
-      <c r="K20" s="1">
+      <c r="J20" s="116"/>
+      <c r="K20" s="103">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -30707,17 +30265,13 @@
         <v>72.64</v>
       </c>
       <c r="G21" s="113"/>
-      <c r="H21" s="114">
-        <v>0</v>
-      </c>
+      <c r="H21" s="114"/>
       <c r="I21" s="115">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J21" s="116">
-        <v>0</v>
-      </c>
-      <c r="K21" s="1">
+      <c r="J21" s="116"/>
+      <c r="K21" s="103">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -31325,7 +30879,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46206</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -31353,7 +30907,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46196</v>
+        <v>46205</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
@@ -31362,7 +30916,7 @@
     </row>
     <row r="6" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="230" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B6" s="230"/>
       <c r="C6" s="230"/>
@@ -31645,18 +31199,14 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G16" s="99"/>
-      <c r="H16" s="100">
-        <v>0</v>
-      </c>
+      <c r="H16" s="100"/>
       <c r="I16" s="101">
         <f>(G16*D16)*F16+H16*F16</f>
         <v>0</v>
       </c>
-      <c r="J16" s="102">
-        <v>0</v>
-      </c>
+      <c r="J16" s="102"/>
       <c r="K16" s="103">
-        <f>I16*$K$13</f>
+        <f>I16*3.5%</f>
         <v>0</v>
       </c>
       <c r="L16" s="104">
@@ -31709,18 +31259,14 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G17" s="113"/>
-      <c r="H17" s="114">
-        <v>0</v>
-      </c>
+      <c r="H17" s="114"/>
       <c r="I17" s="115">
         <f t="shared" ref="I17:I23" si="2">(G17*D17)*F17+H17*F17</f>
         <v>0</v>
       </c>
-      <c r="J17" s="116">
-        <v>0</v>
-      </c>
-      <c r="K17" s="1">
-        <f t="shared" ref="K17:K21" si="3">I17*$K$13</f>
+      <c r="J17" s="116"/>
+      <c r="K17" s="103">
+        <f t="shared" ref="K17:K21" si="3">I17*3.5%</f>
         <v>0</v>
       </c>
       <c r="L17" s="104">
@@ -31773,17 +31319,13 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G18" s="113"/>
-      <c r="H18" s="114">
-        <v>0</v>
-      </c>
+      <c r="H18" s="114"/>
       <c r="I18" s="115">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J18" s="116">
-        <v>0</v>
-      </c>
-      <c r="K18" s="1">
+      <c r="J18" s="116"/>
+      <c r="K18" s="103">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -31833,17 +31375,13 @@
         <v>72.64</v>
       </c>
       <c r="G19" s="113"/>
-      <c r="H19" s="114">
-        <v>0</v>
-      </c>
+      <c r="H19" s="114"/>
       <c r="I19" s="115">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J19" s="116">
-        <v>0</v>
-      </c>
-      <c r="K19" s="1">
+      <c r="J19" s="116"/>
+      <c r="K19" s="103">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -31893,17 +31431,13 @@
         <v>72.64</v>
       </c>
       <c r="G20" s="113"/>
-      <c r="H20" s="114">
-        <v>0</v>
-      </c>
+      <c r="H20" s="114"/>
       <c r="I20" s="115">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J20" s="116">
-        <v>0</v>
-      </c>
-      <c r="K20" s="1">
+      <c r="J20" s="116"/>
+      <c r="K20" s="103">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -31953,17 +31487,13 @@
         <v>72.64</v>
       </c>
       <c r="G21" s="113"/>
-      <c r="H21" s="114">
-        <v>0</v>
-      </c>
+      <c r="H21" s="114"/>
       <c r="I21" s="115">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J21" s="116">
-        <v>0</v>
-      </c>
-      <c r="K21" s="1">
+      <c r="J21" s="116"/>
+      <c r="K21" s="103">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
